--- a/model/Outputs/1. Baseline/Summary.xlsx
+++ b/model/Outputs/1. Baseline/Summary.xlsx
@@ -14,6 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.6" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="250000" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="100000" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4904,4 +4906,812 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AP5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM1" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="AN1" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO1" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="AP1" s="1" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Feed-in Tariffs</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Base NPV</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2275797.145823692</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2275797.145823692</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM1" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="AN1" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO1" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="AP1" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ1" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR1" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS1" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="AT1" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="AU1" s="1" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Prices</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Feed-in Tariffs</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Base NPV</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2275797.145823692</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>